--- a/Tagihan/2026/Juli/Baim PT. Mizan (2).xlsx
+++ b/Tagihan/2026/Juli/Baim PT. Mizan (2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Data Pekerjaan\Tagihan\2026\Juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA7DDB11-D566-4A32-8563-D6596FCAC785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9C10C24-3228-4FB1-B5EA-6ACBC42ECE70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -105,6 +105,15 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
+    <t>No : 100/INV/BNC/VII/2026</t>
+  </si>
+  <si>
+    <t>Ezviz H8C 2MP</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Tanjung, </t>
     </r>
@@ -116,7 +125,7 @@
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t>03</t>
+      <t>27</t>
     </r>
     <r>
       <rPr>
@@ -137,15 +146,6 @@
       </rPr>
       <t>Juli 2026</t>
     </r>
-  </si>
-  <si>
-    <t>No : 100/INV/BNC/VII/2026</t>
-  </si>
-  <si>
-    <t>Ezviz H8C 2MP</t>
-  </si>
-  <si>
-    <t>Unit</t>
   </si>
 </sst>
 </file>
@@ -611,11 +611,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1100,7 +1100,7 @@
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="50" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="50"/>
       <c r="N13" s="6" t="s">
@@ -1108,14 +1108,14 @@
       </c>
     </row>
     <row r="14" spans="2:14" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="51"/>
-      <c r="C14" s="51"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
-      <c r="F14" s="52" t="s">
+      <c r="F14" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="52"/>
+      <c r="G14" s="51"/>
     </row>
     <row r="15" spans="2:14" s="6" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="35"/>
@@ -1123,7 +1123,7 @@
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G15" s="53"/>
     </row>
@@ -1156,13 +1156,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D18" s="14">
         <v>20</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F18" s="27">
         <v>750000</v>
